--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="D2">
-        <v>229</v>
+        <v>313</v>
       </c>
       <c r="E2">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D3">
-        <v>178</v>
+        <v>336</v>
       </c>
       <c r="E3">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>108</v>
       </c>
       <c r="D2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D3">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>426</v>
